--- a/Docs/Cas de tests classement.xlsx
+++ b/Docs/Cas de tests classement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\backup documents\Documents PC commun\Automobilista 2 - Championnats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6435632-429C-4A74-A269-642C3C1D58D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BCE7ED-23CE-4FE3-9855-11CDE1DEEABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{5D2E7F90-A268-49EC-AF10-D36421A37FD7}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -471,6 +472,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -484,12 +491,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -838,64 +839,64 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22">
+      <c r="B1" s="24">
         <v>1</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="22">
+      <c r="C1" s="25"/>
+      <c r="D1" s="24">
         <v>2</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="22">
+      <c r="E1" s="25"/>
+      <c r="F1" s="24">
         <v>3</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="24">
+      <c r="G1" s="25"/>
+      <c r="H1" s="26">
         <v>4</v>
       </c>
-      <c r="I1" s="23"/>
+      <c r="I1" s="25"/>
     </row>
     <row r="2" spans="1:9" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="20" t="s">
+      <c r="C2" s="23"/>
+      <c r="D2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="20" t="s">
+      <c r="E2" s="23"/>
+      <c r="F2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="21"/>
-      <c r="H2" s="20" t="s">
+      <c r="G2" s="23"/>
+      <c r="H2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="21"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="25" t="s">
+      <c r="C3" s="21"/>
+      <c r="D3" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="26"/>
-      <c r="F3" s="25" t="s">
+      <c r="E3" s="21"/>
+      <c r="F3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="26"/>
-      <c r="H3" s="25" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="26"/>
+      <c r="I3" s="21"/>
     </row>
     <row r="4" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1341,7 +1342,7 @@
         <v>7</v>
       </c>
       <c r="I20" s="6">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1368,7 +1369,7 @@
         <v>7</v>
       </c>
       <c r="I21" s="6">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1418,12 +1419,16 @@
         <v>7</v>
       </c>
       <c r="I23" s="8">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D3:E3"/>
@@ -1432,10 +1437,6 @@
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
